--- a/seasonal-class-template.xlsx
+++ b/seasonal-class-template.xlsx
@@ -920,17 +920,17 @@
       <c r="J2" s="43"/>
       <c r="K2" s="44"/>
     </row>
-    <row r="3" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="18"/>
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="15"/>
@@ -944,19 +944,19 @@
       <c r="J4" s="22"/>
       <c r="K4" s="18"/>
     </row>
-    <row r="5" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="18"/>
-    </row>
-    <row r="6" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
@@ -968,437 +968,429 @@
       <c r="J6" s="22"/>
       <c r="K6" s="18"/>
     </row>
-    <row r="7" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H7" s="24"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="27"/>
+    </row>
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C8" s="9"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="29"/>
+    </row>
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H9" s="28"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
+    </row>
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="18"/>
-    </row>
-    <row r="11" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+    </row>
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="18"/>
-    </row>
-    <row r="12" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="29"/>
+    </row>
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="29"/>
+    </row>
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+    </row>
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="18"/>
-    </row>
-    <row r="15" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+    </row>
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="15"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="18"/>
-    </row>
-    <row r="16" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C15" s="32"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="29"/>
+    </row>
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="18"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="18"/>
-    </row>
-    <row r="17" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+    </row>
+    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="18"/>
-    </row>
-    <row r="18" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
+    </row>
+    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="18"/>
-    </row>
-    <row r="19" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="29"/>
+    </row>
+    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="18"/>
-    </row>
-    <row r="20" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="29"/>
+    </row>
+    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="18"/>
-    </row>
-    <row r="21" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="29"/>
+    </row>
+    <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="15"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="18"/>
-    </row>
-    <row r="22" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="18"/>
-    </row>
-    <row r="23" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="27"/>
+    </row>
+    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="18"/>
-    </row>
-    <row r="24" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="9"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="29"/>
+    </row>
+    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="18"/>
-    </row>
-    <row r="25" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C24" s="9"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="29"/>
+    </row>
+    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="18"/>
-    </row>
-    <row r="26" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C25" s="9"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="10"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="29"/>
+    </row>
+    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="18"/>
-    </row>
-    <row r="27" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C26" s="9"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="29"/>
+    </row>
+    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="18"/>
-    </row>
-    <row r="28" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C27" s="9"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="18"/>
-    </row>
-    <row r="29" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C28" s="9"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="10"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="29"/>
+    </row>
+    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="16"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="18"/>
-    </row>
-    <row r="30" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C29" s="9"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="29"/>
+    </row>
+    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="18"/>
-    </row>
-    <row r="31" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C30" s="9"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="29"/>
+    </row>
+    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="18"/>
-    </row>
-    <row r="32" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C31" s="9"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="29"/>
+    </row>
+    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="18"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="18"/>
-    </row>
-    <row r="33" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="9"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="29"/>
+    </row>
+    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="15"/>
       <c r="B33" s="16"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="18"/>
-    </row>
-    <row r="34" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C33" s="9"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="10"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="29"/>
+    </row>
+    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="15"/>
       <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="18"/>
-    </row>
-    <row r="35" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C34" s="9"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="10"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="29"/>
+    </row>
+    <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="15"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="18"/>
-    </row>
-    <row r="36" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C35" s="9"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="10"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="29"/>
+    </row>
+    <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="15"/>
       <c r="B36" s="16"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="18"/>
-    </row>
-    <row r="37" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="9"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="29"/>
+    </row>
+    <row r="37" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="18"/>
-    </row>
-    <row r="38" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C37" s="9"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="10"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="29"/>
+    </row>
+    <row r="38" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="15"/>
       <c r="B38" s="16"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="18"/>
-    </row>
-    <row r="39" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C38" s="9"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="10"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="29"/>
+    </row>
+    <row r="39" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="15"/>
       <c r="B39" s="16"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="18"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="18"/>
-    </row>
-    <row r="40" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C39" s="9"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="10"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="29"/>
+    </row>
+    <row r="40" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="15"/>
       <c r="B40" s="16"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="18"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="18"/>
-    </row>
-    <row r="41" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C40" s="9"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="10"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="29"/>
+    </row>
+    <row r="41" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="15"/>
       <c r="B41" s="16"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="18"/>
-    </row>
-    <row r="42" spans="1:11" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C41" s="9"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="10"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="29"/>
+    </row>
+    <row r="42" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="15"/>
       <c r="B42" s="16"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="18"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="10"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/seasonal-class-template.xlsx
+++ b/seasonal-class-template.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\scheduling-system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8ECCDA-FA20-4FF7-98CE-151C769849D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="範本" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -77,11 +85,11 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="標楷體"/>
-      <family val="4"/>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,7 +100,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -438,21 +446,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -470,7 +463,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -564,31 +557,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -605,6 +577,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -892,20 +867,21 @@
     <col min="1" max="6" width="15" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6328125" style="1" customWidth="1"/>
     <col min="8" max="11" width="12.453125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="40"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="A1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2"/>
@@ -915,10 +891,10 @@
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="44"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
@@ -984,7 +960,7 @@
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="32"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="10"/>
       <c r="H8" s="28"/>
@@ -995,7 +971,7 @@
     <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="16"/>
-      <c r="C9" s="34"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
@@ -1067,7 +1043,7 @@
     <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="15"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="32"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
@@ -1146,17 +1122,17 @@
     </row>
     <row r="22" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="30"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15"/>
       <c r="B23" s="16"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="32"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="H23" s="28"/>
@@ -1168,7 +1144,7 @@
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="32"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
       <c r="H24" s="28"/>
@@ -1180,7 +1156,7 @@
       <c r="A25" s="15"/>
       <c r="B25" s="16"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="32"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
       <c r="H25" s="28"/>
@@ -1192,7 +1168,7 @@
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="32"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
       <c r="H26" s="28"/>
@@ -1204,7 +1180,7 @@
       <c r="A27" s="15"/>
       <c r="B27" s="16"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="32"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="10"/>
       <c r="H27" s="28"/>
@@ -1216,7 +1192,7 @@
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="32"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
       <c r="H28" s="28"/>
@@ -1228,7 +1204,7 @@
       <c r="A29" s="15"/>
       <c r="B29" s="16"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="32"/>
+      <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="10"/>
       <c r="H29" s="28"/>
@@ -1240,7 +1216,7 @@
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="32"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="10"/>
       <c r="H30" s="28"/>
@@ -1252,7 +1228,7 @@
       <c r="A31" s="15"/>
       <c r="B31" s="16"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="32"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="10"/>
       <c r="H31" s="28"/>
@@ -1264,7 +1240,7 @@
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="32"/>
+      <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="10"/>
       <c r="H32" s="28"/>
@@ -1276,7 +1252,7 @@
       <c r="A33" s="15"/>
       <c r="B33" s="16"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="32"/>
+      <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="10"/>
       <c r="H33" s="28"/>
@@ -1288,7 +1264,7 @@
       <c r="A34" s="15"/>
       <c r="B34" s="16"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="32"/>
+      <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="10"/>
       <c r="H34" s="28"/>
@@ -1300,7 +1276,7 @@
       <c r="A35" s="15"/>
       <c r="B35" s="16"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="32"/>
+      <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="10"/>
       <c r="H35" s="28"/>
@@ -1312,7 +1288,7 @@
       <c r="A36" s="15"/>
       <c r="B36" s="16"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="32"/>
+      <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="10"/>
       <c r="H36" s="28"/>
@@ -1324,7 +1300,7 @@
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="32"/>
+      <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="10"/>
       <c r="H37" s="28"/>
@@ -1336,7 +1312,7 @@
       <c r="A38" s="15"/>
       <c r="B38" s="16"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="32"/>
+      <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="10"/>
       <c r="H38" s="28"/>
@@ -1348,7 +1324,7 @@
       <c r="A39" s="15"/>
       <c r="B39" s="16"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="32"/>
+      <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="10"/>
       <c r="H39" s="28"/>
@@ -1360,7 +1336,7 @@
       <c r="A40" s="15"/>
       <c r="B40" s="16"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="32"/>
+      <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="10"/>
       <c r="H40" s="28"/>
@@ -1372,7 +1348,7 @@
       <c r="A41" s="15"/>
       <c r="B41" s="16"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="32"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="10"/>
       <c r="H41" s="28"/>
@@ -1384,7 +1360,7 @@
       <c r="A42" s="15"/>
       <c r="B42" s="16"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="32"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="10"/>
       <c r="H42" s="28"/>
@@ -1400,6 +1376,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="62" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" scale="62" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>